--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260731.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.91%</t>
+          <t>3.89%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.55%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,820,000</t>
+          <t>46,121,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>46,121,000</t>
+          <t>5,972,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>34,303,000</t>
+          <t>35,274,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -765,34 +765,34 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>20,517,000</t>
+          <t>21,105,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>24,881,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -809,78 +809,78 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>33,157,000</t>
+          <t>34,365,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>25,898,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>30,079,000</t>
+          <t>19,587,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>19,587,000</t>
+          <t>30,079,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>9,446,000</t>
+          <t>9,520,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -990,117 +990,117 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,151,000</t>
+          <t>20,683,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>20,683,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>2,847,538,544</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>2,169,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,519,407,937</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -1188,73 +1188,73 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>9,574,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>9,574,000</t>
+          <t>2,384,425,322</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1271,29 +1271,29 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>5,666,000</t>
+          <t>5,975,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,971,505,322</t>
+          <t>518,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,110 +1305,110 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>518,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>3,498,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>3,498,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1496,68 +1496,68 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,575,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>7,223,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>7,223,000</t>
+          <t>1,575,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,83 +1569,83 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>47,231,000</t>
+          <t>2,088,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>47,231,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2,088,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>18,691,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,44 +1657,44 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>17,282,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,691,000</t>
+          <t>18,174,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-18,301,118</t>
+          <t>-31,958,960</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
     </row>
